--- a/content/roster.xlsx
+++ b/content/roster.xlsx
@@ -54,7 +54,8 @@
     <col min="10" max="10" width="30" customWidth="1"/>
     <col min="11" max="11" width="24" customWidth="1"/>
     <col min="12" max="12" width="34" customWidth="1"/>
-    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="13" max="13" width="26" customWidth="1"/>
+    <col min="14" max="14" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -120,6 +121,11 @@
       </c>
       <c r="M1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">endsRunChance (0-1, blank = certain)</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">reviewed (TRUE/FALSE)</t>
         </is>
       </c>
@@ -180,7 +186,7 @@
           <t xml:space="preserve">leopold-ii</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -237,7 +243,7 @@
           <t xml:space="preserve">beloved, statesman, loyalist</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -299,7 +305,7 @@
           <t xml:space="preserve">chamberlain</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -361,7 +367,7 @@
           <t xml:space="preserve">pinochet</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -423,7 +429,7 @@
           <t xml:space="preserve">vlad</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -480,7 +486,7 @@
           <t xml:space="preserve">statesman, soldier, strategist</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -537,7 +543,7 @@
           <t xml:space="preserve">statesman, technocrat, loyalist</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -594,7 +600,7 @@
           <t xml:space="preserve">statesman, beloved, strategist</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -651,7 +657,7 @@
           <t xml:space="preserve">statesman, cunning, showman</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -708,7 +714,7 @@
           <t xml:space="preserve">beloved, showman, statesman</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -765,7 +771,7 @@
           <t xml:space="preserve">beloved, statesman, dealmaker</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -822,7 +828,7 @@
           <t xml:space="preserve">technocrat, statesman, strategist</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -879,7 +885,7 @@
           <t xml:space="preserve">technocrat, statesman, loyalist</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -941,7 +947,7 @@
           <t xml:space="preserve">pinochet</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -998,7 +1004,7 @@
           <t xml:space="preserve">beloved, statesman, showman</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -1055,7 +1061,7 @@
           <t xml:space="preserve">statesman, warhawk, strategist</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -1112,7 +1118,7 @@
           <t xml:space="preserve">soldier, showman, statesman</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -1169,7 +1175,7 @@
           <t xml:space="preserve">soldier, strategist, statesman</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -1226,7 +1232,7 @@
           <t xml:space="preserve">dealmaker, statesman, beloved</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -1283,7 +1289,7 @@
           <t xml:space="preserve">beloved, statesman, soldier</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -1345,7 +1351,7 @@
           <t xml:space="preserve">Eighteen and a half minutes of the tape are missing. So is your government.</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -1402,7 +1408,7 @@
           <t xml:space="preserve">warhawk, soldier, strategist</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -1464,7 +1470,7 @@
           <t xml:space="preserve">robespierre</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -1521,7 +1527,7 @@
           <t xml:space="preserve">demagogue, strategist, paranoid</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -1578,7 +1584,7 @@
           <t xml:space="preserve">paranoid, demagogue, isolationist</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -1635,7 +1641,7 @@
           <t xml:space="preserve">demagogue, showman, warhawk</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -1692,7 +1698,7 @@
           <t xml:space="preserve">paranoid, soldier, isolationist</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -1749,7 +1755,7 @@
           <t xml:space="preserve">showman, warhawk, paranoid</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -1806,7 +1812,7 @@
           <t xml:space="preserve">paranoid, demagogue, showman</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -1868,7 +1874,7 @@
           <t xml:space="preserve">allende, mandela</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -1925,7 +1931,7 @@
           <t xml:space="preserve">demagogue, paranoid, showman</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -1982,7 +1988,7 @@
           <t xml:space="preserve">paranoid, demagogue, cunning</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -2039,7 +2045,7 @@
           <t xml:space="preserve">showman, demagogue, paranoid</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -2096,7 +2102,7 @@
           <t xml:space="preserve">paranoid, warhawk, demagogue</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -2153,7 +2159,7 @@
           <t xml:space="preserve">showman, warhawk, paranoid</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -2210,7 +2216,7 @@
           <t xml:space="preserve">cunning, showman, dealmaker</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -2267,7 +2273,7 @@
           <t xml:space="preserve">cunning, demagogue, banker</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -2324,7 +2330,7 @@
           <t xml:space="preserve">showman, demagogue, paranoid</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -2386,7 +2392,7 @@
           <t xml:space="preserve">lincoln</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -2443,7 +2449,7 @@
           <t xml:space="preserve">showman, paranoid, demagogue</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -2505,7 +2511,7 @@
           <t xml:space="preserve">gandhi</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -2567,7 +2573,7 @@
           <t xml:space="preserve">stalin</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -2629,7 +2635,7 @@
           <t xml:space="preserve">churchill</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -2686,7 +2692,7 @@
           <t xml:space="preserve">strategist, cunning, statesman</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -2748,7 +2754,7 @@
           <t xml:space="preserve">crassus</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -2805,7 +2811,7 @@
           <t xml:space="preserve">dealmaker, showman, cunning</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -2862,7 +2868,7 @@
           <t xml:space="preserve">technocrat, banker, scandal-magnet</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -2919,7 +2925,7 @@
           <t xml:space="preserve">demagogue, showman, scandal-magnet</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -2981,7 +2987,7 @@
           <t xml:space="preserve">caesar</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -3038,7 +3044,7 @@
           <t xml:space="preserve">dealmaker, cunning, loyalist</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -3095,7 +3101,7 @@
           <t xml:space="preserve">showman, soldier, paranoid</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -3152,7 +3158,7 @@
           <t xml:space="preserve">showman, beloved, loyalist</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -3209,7 +3215,7 @@
           <t xml:space="preserve">banker, dealmaker, showman</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -3266,7 +3272,7 @@
           <t xml:space="preserve">warhawk, soldier, showman</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -3323,7 +3329,7 @@
           <t xml:space="preserve">beloved, statesman, loyalist</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -3380,7 +3386,7 @@
           <t xml:space="preserve">warhawk, soldier, paranoid, strategist</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -3437,7 +3443,7 @@
           <t xml:space="preserve">beloved, loyalist, statesman</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -3494,7 +3500,7 @@
           <t xml:space="preserve">dealmaker, beloved, loyalist</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -3551,7 +3557,7 @@
           <t xml:space="preserve">isolationist, soldier, beloved</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -3613,7 +3619,7 @@
           <t xml:space="preserve">sauron</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -3675,7 +3681,7 @@
           <t xml:space="preserve">gandalf, optimus-prime</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -3732,7 +3738,7 @@
           <t xml:space="preserve">statesman, strategist, loyalist</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -3794,7 +3800,7 @@
           <t xml:space="preserve">joker</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -3856,7 +3862,7 @@
           <t xml:space="preserve">batman</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -3918,7 +3924,7 @@
           <t xml:space="preserve">mr-burns</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -3980,7 +3986,7 @@
           <t xml:space="preserve">homer-simpson</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -4037,7 +4043,7 @@
           <t xml:space="preserve">beloved, loyalist, showman</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -4094,7 +4100,7 @@
           <t xml:space="preserve">liability, beloved, loyalist</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -4156,7 +4162,7 @@
           <t xml:space="preserve">mario</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -4218,7 +4224,7 @@
           <t xml:space="preserve">bowser</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -4275,7 +4281,7 @@
           <t xml:space="preserve">warhawk, soldier, isolationist</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -4337,7 +4343,7 @@
           <t xml:space="preserve">sauron</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -4394,7 +4400,7 @@
           <t xml:space="preserve">warhawk, technocrat, strategist</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -4451,7 +4457,7 @@
           <t xml:space="preserve">technocrat, paranoid, cunning</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -4508,7 +4514,7 @@
           <t xml:space="preserve">technocrat, cunning, demagogue</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -4565,7 +4571,7 @@
           <t xml:space="preserve">strategist, technocrat, paranoid</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -4622,7 +4628,7 @@
           <t xml:space="preserve">cunning, showman, isolationist</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -4679,7 +4685,7 @@
           <t xml:space="preserve">beloved, loyalist, liability</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -4736,7 +4742,7 @@
           <t xml:space="preserve">paranoid, cunning, liability</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -4793,7 +4799,7 @@
           <t xml:space="preserve">paranoid, demagogue, warhawk</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -4850,7 +4856,7 @@
           <t xml:space="preserve">cunning, technocrat, paranoid</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -4907,7 +4913,7 @@
           <t xml:space="preserve">isolationist, warhawk, paranoid</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -4964,7 +4970,7 @@
           <t xml:space="preserve">liability, loyalist, beloved</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
+      <c r="N84" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -5021,7 +5027,7 @@
           <t xml:space="preserve">soldier, showman, beloved</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="N85" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -5078,7 +5084,7 @@
           <t xml:space="preserve">paranoid, loyalist, liability</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="N86" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -5135,7 +5141,7 @@
           <t xml:space="preserve">technocrat, soldier, loyalist</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="N87" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -5192,7 +5198,7 @@
           <t xml:space="preserve">showman, technocrat, scandal-magnet</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr">
+      <c r="N88" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -5249,7 +5255,7 @@
           <t xml:space="preserve">showman, dealmaker, beloved</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
+      <c r="N89" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -5306,7 +5312,7 @@
           <t xml:space="preserve">beloved, showman, soldier</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr">
+      <c r="N90" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -5363,7 +5369,7 @@
           <t xml:space="preserve">beloved, dealmaker, showman</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
+      <c r="N91" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -5420,7 +5426,7 @@
           <t xml:space="preserve">beloved, statesman, technocrat</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr">
+      <c r="N92" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -5477,7 +5483,7 @@
           <t xml:space="preserve">beloved, soldier, showman</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr">
+      <c r="N93" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -5534,7 +5540,7 @@
           <t xml:space="preserve">beloved, statesman, loyalist</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr">
+      <c r="N94" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -5591,7 +5597,7 @@
           <t xml:space="preserve">technocrat, showman, soldier</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr">
+      <c r="N95" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -5648,7 +5654,7 @@
           <t xml:space="preserve">technocrat, paranoid, strategist</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr">
+      <c r="N96" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -5705,7 +5711,7 @@
           <t xml:space="preserve">technocrat, statesman, beloved</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr">
+      <c r="N97" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -5762,7 +5768,7 @@
           <t xml:space="preserve">technocrat, strategist, banker</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr">
+      <c r="N98" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -5819,7 +5825,7 @@
           <t xml:space="preserve">technocrat, loyalist, statesman</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr">
+      <c r="N99" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -5876,7 +5882,7 @@
           <t xml:space="preserve">technocrat, strategist, loyalist</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr">
+      <c r="N100" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -5933,7 +5939,7 @@
           <t xml:space="preserve">statesman, beloved, technocrat</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr">
+      <c r="N101" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -5990,7 +5996,7 @@
           <t xml:space="preserve">showman, dealmaker, beloved</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr">
+      <c r="N102" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -6047,7 +6053,7 @@
           <t xml:space="preserve">showman, soldier, liability</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr">
+      <c r="N103" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -6104,7 +6110,7 @@
           <t xml:space="preserve">statesman, strategist, isolationist</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr">
+      <c r="N104" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -6161,7 +6167,7 @@
           <t xml:space="preserve">showman, beloved, demagogue</t>
         </is>
       </c>
-      <c r="M105" t="inlineStr">
+      <c r="N105" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -6218,7 +6224,7 @@
           <t xml:space="preserve">soldier, showman, strategist</t>
         </is>
       </c>
-      <c r="M106" t="inlineStr">
+      <c r="N106" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -6275,7 +6281,7 @@
           <t xml:space="preserve">demagogue, showman, scandal-magnet</t>
         </is>
       </c>
-      <c r="M107" t="inlineStr">
+      <c r="N107" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -6332,7 +6338,7 @@
           <t xml:space="preserve">statesman, soldier, technocrat</t>
         </is>
       </c>
-      <c r="M108" t="inlineStr">
+      <c r="N108" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -6389,7 +6395,7 @@
           <t xml:space="preserve">demagogue, cunning, showman</t>
         </is>
       </c>
-      <c r="M109" t="inlineStr">
+      <c r="N109" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -6446,7 +6452,7 @@
           <t xml:space="preserve">showman, dealmaker, banker</t>
         </is>
       </c>
-      <c r="M110" t="inlineStr">
+      <c r="N110" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -6503,7 +6509,7 @@
           <t xml:space="preserve">showman, demagogue, soldier</t>
         </is>
       </c>
-      <c r="M111" t="inlineStr">
+      <c r="N111" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -6560,7 +6566,7 @@
           <t xml:space="preserve">dealmaker, banker, loyalist</t>
         </is>
       </c>
-      <c r="M112" t="inlineStr">
+      <c r="N112" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -6617,7 +6623,7 @@
           <t xml:space="preserve">statesman, strategist, paranoid</t>
         </is>
       </c>
-      <c r="M113" t="inlineStr">
+      <c r="N113" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -6674,7 +6680,7 @@
           <t xml:space="preserve">loyalist, technocrat, liability</t>
         </is>
       </c>
-      <c r="M114" t="inlineStr">
+      <c r="N114" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -6731,7 +6737,7 @@
           <t xml:space="preserve">paranoid, technocrat, banker</t>
         </is>
       </c>
-      <c r="M115" t="inlineStr">
+      <c r="N115" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -6788,7 +6794,7 @@
           <t xml:space="preserve">loyalist, liability, soldier</t>
         </is>
       </c>
-      <c r="M116" t="inlineStr">
+      <c r="N116" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -6845,7 +6851,7 @@
           <t xml:space="preserve">technocrat, loyalist, liability</t>
         </is>
       </c>
-      <c r="M117" t="inlineStr">
+      <c r="N117" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -6902,7 +6908,7 @@
           <t xml:space="preserve">technocrat, isolationist, liability</t>
         </is>
       </c>
-      <c r="M118" t="inlineStr">
+      <c r="N118" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -6959,7 +6965,7 @@
           <t xml:space="preserve">loyalist, paranoid, liability</t>
         </is>
       </c>
-      <c r="M119" t="inlineStr">
+      <c r="N119" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -7016,7 +7022,7 @@
           <t xml:space="preserve">cunning, loyalist, scandal-magnet</t>
         </is>
       </c>
-      <c r="M120" t="inlineStr">
+      <c r="N120" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -7073,7 +7079,7 @@
           <t xml:space="preserve">banker, dealmaker, scandal-magnet</t>
         </is>
       </c>
-      <c r="M121" t="inlineStr">
+      <c r="N121" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -7130,7 +7136,7 @@
           <t xml:space="preserve">warhawk, soldier, paranoid</t>
         </is>
       </c>
-      <c r="M122" t="inlineStr">
+      <c r="N122" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
@@ -7187,14 +7193,14 @@
           <t xml:space="preserve">liability, loyalist, beloved</t>
         </is>
       </c>
-      <c r="M123" t="inlineStr">
+      <c r="N123" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUE</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M123"/>
+  <autoFilter ref="A1:N123"/>
 </worksheet>
 </file>
 

--- a/content/roster.xlsx
+++ b/content/roster.xlsx
@@ -1338,7 +1338,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Appointing him ends your government immediately. He has done this before.</t>
+          <t xml:space="preserve">Appointing him usually works out. He has ended a government before, and would rather not discuss the odds.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1349,6 +1349,11 @@
       <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">Eighteen and a half minutes of the tape are missing. So is your government.</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.1</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -7199,8 +7204,2117 @@
         </is>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">charlie-kirk</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Charlie Kirk</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politician</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operator</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">neutral</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United States</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020s</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Commentator, Campus Organiser</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Built a movement out of arguing with undergraduates on their own lawns.</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">demagogue, showman, strategist</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nine-eleven</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nine Eleven</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">object</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">titan</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bad</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United States</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2000s</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Date Itself</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Requires no introduction and will not be providing one.</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paranoid, warhawk, statesman</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diddy</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diddy</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wildcard</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heavyweight</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bad</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United States</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modern</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Producer, Label Executive</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Built an empire on other people's records and put his own name on the sleeve.</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dealmaker, showman, scandal-magnet</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">soju-bottle</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Soju Bottle</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">object</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">liability</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">neutral</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fictional</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modern</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Refreshment</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Green, cheap, and responsible for more foreign policy than anyone will admit.</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dealmaker, liability, beloved</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epstein</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jeffrey Epstein</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politician</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flawed</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bad</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United States</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2000s</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Financier</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Managed money nobody could name for clients nobody would name.</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cunning, dealmaker, scandal-magnet</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hun-sen</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hun Sen</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politician</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heavyweight</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bad</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cambodia</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1990s</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prime Minister</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Held the office for thirty-eight years and called every one of them a mandate.</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cunning, paranoid, strategist</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trump</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Donald Trump</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politician</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heavyweight</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bad</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United States</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020s</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">President</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Says the quiet part at length, on a stage, to applause.</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">demagogue, showman, dealmaker</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">time-passing</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Concept of Time Passing</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">object</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">titan</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">neutral</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fictional</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modern</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inevitability</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attends every meeting. Resolves every crisis eventually, at a cost.</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">statesman, strategist, isolationist</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xi-jinping</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Xi Jinping</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politician</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">titan</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bad</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020s</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">General Secretary</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removed the term limit, then removed the discussion about removing the term limit.</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cunning, paranoid, strategist</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kai-cenat</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kai Cenat</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wildcard</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operator</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">neutral</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United States</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Internet</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Streamer</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Can hold an audience for thirty days without once leaving the room.</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">showman, beloved, liability</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">four-horsemen</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Four Horsemen of the Apocalypse</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wildcard</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">titan</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bad</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fictional</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fictional</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Death, War, Famine and Pestilence</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Four applicants, one post, and a portfolio that overlaps considerably.</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">warhawk, soldier, paranoid</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eye-of-cthulhu</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Eye of Cthulhu</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wildcard</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flawed</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bad</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fictional</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fictional</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nocturnal Menace</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arrives on the first night uninvited and leaves the furniture rearranged.</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">warhawk, paranoid, liability</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">erika-kirk</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erika Kirk</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politician</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operator</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">neutral</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United States</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020s</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Executive, Author</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inherited an organisation and a great deal of unsolicited advice about it.</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">loyalist, statesman, beloved</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chatgpt</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ChatGPT</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wildcard</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heavyweight</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">neutral</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United States</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Internet</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Language Model</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Will answer anything immediately, at length, and with total confidence.</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">technocrat, showman, liability</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brazil-germany</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brasil v Germany 7-1</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">object</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">liability</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bad</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brazil</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2010s</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Result</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Still the reason a nation flinches at the number seven.</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">liability, scandal-magnet, soldier</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lamine-yamal</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lamine Yamal</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wildcard</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operator</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">good</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spain</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modern</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Footballer</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solved problems at seventeen that the room had been failing at for a decade.</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">beloved, strategist, showman</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">messi</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lionel Messi</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wildcard</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">titan</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">good</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Argentina</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modern</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Footballer</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Says almost nothing, does the impossible on Tuesdays, goes home to his family.</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">beloved, strategist, loyalist</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ronaldo</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cristiano Ronaldo</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wildcard</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">titan</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">neutral</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Portugal</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modern</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Footballer</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Has never once doubted himself and considers this a policy position.</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">showman, soldier, beloved</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">infantino</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gianni Infantino</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politician</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operator</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bad</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Switzerland</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modern</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Football Administrator</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Awards the tournament to whoever asks most generously.</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dealmaker, cunning, scandal-magnet</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hitler</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adolf Hitler</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politician</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heavyweight</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bad</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Germany</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1930s</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chancellor</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failed at art school and made it comprehensively everybody else's problem.</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">demagogue, warhawk, paranoid</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the-fog</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Fog</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">object</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heavyweight</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">neutral</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fictional</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modern</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Weather</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Is coming. Has been coming for some time. Will be here shortly.</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">isolationist, paranoid, strategist</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lelouch</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lelouch vi Britannia</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wildcard</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">titan</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bad</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fictional</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fictional</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exiled Prince, Terrorist</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wins by ordering the room to agree, then wins again by having planned that.</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cunning, strategist, demagogue</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marlboro-tropical</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Pack of Marlboro 8 Tropical Blast</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">object</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">liability</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">neutral</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fictional</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modern</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Personal Effects</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Somebody's favourite. Not doing anybody any good.</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">beloved, liability, dealmaker</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">airfryer</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An Air Fryer</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">object</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operator</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">good</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fictional</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modern</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kitchen Equipment</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Top three inventions of all time and it will hear no argument.</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">technocrat, beloved, loyalist</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the-backrooms</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Backrooms</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wildcard</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heavyweight</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bad</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fictional</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Internet</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Endless Office Space</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Six hundred million square feet of civil service and no exit.</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">isolationist, paranoid, technocrat</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a-real-bear</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bear (a real bear)</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wildcard</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heavyweight</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">neutral</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fictional</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modern</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bear</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Is a bear. Was not consulted about the appointment and does not know of it.</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">soldier, liability, isolationist</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">traore</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ibrahim Traore</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politician</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operator</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">neutral</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Burkina Faso</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020s</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interim President</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Took power at thirty-four and was gifted two hundred pregnant cows for it.</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">soldier, demagogue, strategist</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">triple-t</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Triple T</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wildcard</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flawed</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">neutral</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fictional</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Internet</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tung Tung Tung Sahur</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bangs the drum before dawn until somebody answers the door.</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">demagogue, showman, liability</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yellow-bear</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yellow Bear</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wildcard</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flawed</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bad</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fictional</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fictional</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Golden Freddy, Reportedly</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Appears in the room when nobody has opened a door, and is sitting down.</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paranoid, liability, showman</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spherical-cow</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Spherical Cow</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">object</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operator</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">neutral</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fictional</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modern</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modelling Assumption</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Makes the numbers work, in a vacuum, given a frictionless surface.</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">technocrat, strategist, liability</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">friends-house</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">My Friend's House</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">object</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operator</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">good</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fictional</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modern</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A House</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He lives there. Everyone has been. It has always been fine.</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">beloved, loyalist, isolationist</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ye</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ye</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wildcard</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heavyweight</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bad</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United States</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modern</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Musician, Designer</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Produces something extraordinary, then produces a statement about it.</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">showman, demagogue, scandal-magnet</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tiktok-jack</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jack from TikTok Movie Summaries</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wildcard</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flawed</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">neutral</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fictional</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Internet</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Protagonist</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Is the male lead of every film summarised in ninety seconds by a synthetic voice.</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">beloved, liability, loyalist</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">druski</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Druski</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wildcard</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operator</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">neutral</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United States</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Internet</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comedian</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turns up in character, in costume, and refuses to break for anyone.</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">showman, beloved, cunning</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bible</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Bible</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">object</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">titan</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">neutral</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fictional</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modern</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Book</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Has been cited in support of every position the cabinet has ever taken.</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">statesman, beloved, strategist</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dr-house</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dr House</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wildcard</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heavyweight</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">neutral</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fictional</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fictional</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diagnostician</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Is right, is insufferable, and will not do the second one less to prove the first.</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">technocrat, cunning, liability</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marsupial-lion</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Marsupial Lion</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wildcard</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operator</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">neutral</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Australia</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fictional</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Extinct Predator</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bit harder than anything alive and has been unavailable for comment since.</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">soldier, warhawk, isolationist</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N123"/>
+  <autoFilter ref="A1:N160"/>
 </worksheet>
 </file>
 
